--- a/data/analysis_qwen2_audio/sound_event_eval_qwen2_audio_w1_0s_h1_0s.xlsx
+++ b/data/analysis_qwen2_audio/sound_event_eval_qwen2_audio_w1_0s_h1_0s.xlsx
@@ -22,13 +22,19 @@
     <sheet name="Scene_15" sheetId="13" r:id="rId13"/>
     <sheet name="Scene_16" sheetId="14" r:id="rId14"/>
     <sheet name="Scene_17" sheetId="15" r:id="rId15"/>
+    <sheet name="Scene_29" sheetId="16" r:id="rId16"/>
+    <sheet name="Scene_30" sheetId="17" r:id="rId17"/>
+    <sheet name="Scene_31" sheetId="18" r:id="rId18"/>
+    <sheet name="Scene_32" sheetId="19" r:id="rId19"/>
+    <sheet name="Scene_33" sheetId="20" r:id="rId20"/>
+    <sheet name="Scene_34" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="44">
   <si>
     <t>event</t>
   </si>
@@ -139,6 +145,27 @@
   </si>
   <si>
     <t>engine(0-24), horn(24-48), shout(48-72), shout(120-168), impact(72-120), impact(168-240)</t>
+  </si>
+  <si>
+    <t>shout(0-216), impact(216-240)</t>
+  </si>
+  <si>
+    <t>shout(0-216), gunshot_or_explosion(120-144), impact(216-240)</t>
+  </si>
+  <si>
+    <t>impact(0-144), shout(24-48), shout(144-240), impact(192-216)</t>
+  </si>
+  <si>
+    <t>impact(0-24), shout(24-192), impact(72-144), impact(192-240)</t>
+  </si>
+  <si>
+    <t>engine(0-24), horn(24-72), impact(72-96), gunshot_or_explosion(96-120), shout(120-144), impact(144-240)</t>
+  </si>
+  <si>
+    <t>engine(0-24), horn(24-72), impact(72-96), impact(144-240), gunshot_or_explosion(96-120), shout(120-144)</t>
+  </si>
+  <si>
+    <t>tire_squeal(0-24), shout(24-48), impact(48-240), shout(96-120), shout(192-216)</t>
   </si>
 </sst>
 </file>
@@ -1000,6 +1027,199 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
@@ -1037,6 +1257,111 @@
       </c>
       <c r="E2" t="s">
         <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/data/analysis_qwen2_audio/sound_event_eval_qwen2_audio_w1_0s_h1_0s.xlsx
+++ b/data/analysis_qwen2_audio/sound_event_eval_qwen2_audio_w1_0s_h1_0s.xlsx
@@ -612,19 +612,19 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="D4">
-        <v>0.75</v>
+        <v>0.333</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -840,10 +840,10 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
@@ -996,10 +996,10 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
       <c r="E2" t="s">
         <v>35</v>
